--- a/EXCEL TERBARU.xlsx
+++ b/EXCEL TERBARU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jefri-up\MIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8591941-86A5-48D9-8DCE-7364A0C974AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCA42B4-34A4-4AE8-9DDB-A3CBC013C40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" tabRatio="888" firstSheet="2" activeTab="2" xr2:uid="{77A85E82-D8F6-4D70-9B3E-9548D31FE4F7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="888" firstSheet="2" activeTab="2" xr2:uid="{77A85E82-D8F6-4D70-9B3E-9548D31FE4F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary (2)" sheetId="4" state="hidden" r:id="rId1"/>
@@ -907,9 +907,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="19" x14ac:knownFonts="1">
     <font>
@@ -1660,21 +1660,21 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1693,14 +1693,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1719,8 +1719,8 @@
     <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1730,25 +1730,25 @@
     <xf numFmtId="1" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="15" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
@@ -1757,17 +1757,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1786,7 +1786,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
@@ -1799,7 +1799,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
@@ -1809,41 +1809,41 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1853,7 +1853,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1861,30 +1861,30 @@
     <xf numFmtId="1" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="16" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="14" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1894,7 +1894,7 @@
     <xf numFmtId="0" fontId="8" fillId="14" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="14" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1904,109 +1904,109 @@
     <xf numFmtId="1" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="16" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="15" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="4" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="15" fontId="17" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="17" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -2014,7 +2014,7 @@
     <xf numFmtId="1" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -2023,13 +2023,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="4" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="17" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="15" fontId="4" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="17" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2039,37 +2039,37 @@
     <xf numFmtId="1" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="18" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="4" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="18" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="20" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="17" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="4" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="17" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="20" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="0" fillId="20" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="20" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="15" fontId="17" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2077,10 +2077,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2160,10 +2160,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2190,10 +2190,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2242,9 +2242,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2282,7 +2282,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2388,7 +2388,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2530,7 +2530,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -30925,10 +30925,10 @@
     <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.42578125" customWidth="1"/>
     <col min="3" max="3" width="16.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" style="29" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" style="29" customWidth="1"/>
     <col min="6" max="6" width="16.140625" style="29" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" customWidth="1"/>
     <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.85546875" customWidth="1"/>
@@ -32494,7 +32494,7 @@
         <v>342500000</v>
       </c>
       <c r="M23" s="55">
-        <f t="shared" ref="M23:M36" si="17">(L23*20%)/H23</f>
+        <f t="shared" ref="M23:M35" si="17">(L23*20%)/H23</f>
         <v>68500000</v>
       </c>
       <c r="N23" s="56">
